--- a/diseases/d042/1980-1984.xlsx
+++ b/diseases/d042/1980-1984.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14519,9 +14414,6 @@
       </c>
       <c r="O72" t="n">
         <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>

--- a/diseases/d042/1980-1984.xlsx
+++ b/diseases/d042/1980-1984.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1980-02-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1980-02</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1980-02-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1980-02</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1980-03-01</t>
+          <t>1980-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1980-03</t>
+          <t>1980-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1980-03-01</t>
+          <t>1980-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1980-03</t>
+          <t>1980-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1980-04-01</t>
+          <t>1980-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1980-04</t>
+          <t>1980-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1980-04-01</t>
+          <t>1980-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1980-04</t>
+          <t>1980-03</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2311,19 +2311,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1980-05-01</t>
+          <t>1980-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1980-05</t>
+          <t>1980-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2467,19 +2467,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1980-05-01</t>
+          <t>1980-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1980-05</t>
+          <t>1980-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2701,19 +2701,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1980-06-01</t>
+          <t>1980-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1980-06</t>
+          <t>1980-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2857,19 +2857,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1980-06-01</t>
+          <t>1980-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1980-06</t>
+          <t>1980-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1980-07-01</t>
+          <t>1980-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1980-07</t>
+          <t>1980-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1980-07-01</t>
+          <t>1980-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1980-07</t>
+          <t>1980-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1980-08-01</t>
+          <t>1980-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1980-08</t>
+          <t>1980-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1980-08-01</t>
+          <t>1980-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1980-08</t>
+          <t>1980-07</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3871,19 +3871,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1980-09-01</t>
+          <t>1980-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1980-09</t>
+          <t>1980-08</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -4027,19 +4027,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1980-09-01</t>
+          <t>1980-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1980-09</t>
+          <t>1980-08</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4261,19 +4261,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1980-10-01</t>
+          <t>1980-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1980-10</t>
+          <t>1980-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1980-10-01</t>
+          <t>1980-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1980-10</t>
+          <t>1980-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1980-11-01</t>
+          <t>1980-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1980-11</t>
+          <t>1980-10</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1980-11-01</t>
+          <t>1980-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1980-11</t>
+          <t>1980-10</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1980-12-01</t>
+          <t>1980-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1980-12</t>
+          <t>1980-11</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1980-12-01</t>
+          <t>1980-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1980-12</t>
+          <t>1980-11</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1980-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1980-12</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1980-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1980-12</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,19 +5821,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +5880,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +5947,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,38 +5977,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6114,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6232,12 +6232,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -6270,42 +6270,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6367,38 +6367,38 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6601,19 +6601,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -6660,42 +6660,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6757,38 +6757,38 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6894,42 +6894,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7771,19 +7771,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7927,19 +7927,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -10267,12 +10267,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11671,19 +11671,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11730,42 +11730,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11827,38 +11827,38 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_503_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D64_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -11964,42 +11964,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12061,12 +12061,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -12607,12 +12607,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -12841,19 +12841,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12997,19 +12997,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13231,12 +13231,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -13387,12 +13387,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -14401,19 +14401,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14557,19 +14557,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14728,6 +14728,1956 @@
         </is>
       </c>
       <c r="BC73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1984-08-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1984-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1984-08-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1984-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1984-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1984-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1984-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1984-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Lepra</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_503_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -14849,7 +16799,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14859,7 +16809,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -14879,7 +16829,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -14889,7 +16839,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -14911,7 +16861,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
